--- a/memory/EFYL_QA_Test_Script_FR_EN.xlsx
+++ b/memory/EFYL_QA_Test_Script_FR_EN.xlsx
@@ -516,7 +516,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>EFYL Address Book — Script de tests QA (FR)</t>
+          <t>EFYL AddressBook — Script de tests QA (FR)</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>EFYL Address Book — QA test script (EN)</t>
+          <t>EFYL AddressBook — QA test script (EN)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
